--- a/Excel/10_SolidWaste_WIP_v02.xlsx
+++ b/Excel/10_SolidWaste_WIP_v02.xlsx
@@ -650,9 +650,9 @@
       <rPr>
         <b/>
         <vertAlign val="subscript"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color rgb="FF183C1B"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>wt</t>
@@ -666,9 +666,9 @@
       <rPr>
         <b/>
         <vertAlign val="subscript"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color rgb="FF183C1B"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>w</t>
@@ -738,9 +738,9 @@
     <r>
       <rPr>
         <b/>
-        <sz val="16"/>
+        <sz val="14"/>
         <color theme="1" tint="0.24994659260841701"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>E</t>
@@ -749,9 +749,9 @@
       <rPr>
         <b/>
         <vertAlign val="subscript"/>
-        <sz val="16"/>
+        <sz val="14"/>
         <color theme="1" tint="0.24994659260841701"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>g</t>
@@ -858,9 +858,9 @@
       <rPr>
         <b/>
         <vertAlign val="subscript"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color rgb="FF183C1B"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>g</t>
@@ -874,9 +874,9 @@
       <rPr>
         <b/>
         <vertAlign val="subscript"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color rgb="FF183C1B"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>wtg</t>
@@ -890,9 +890,9 @@
       <rPr>
         <b/>
         <vertAlign val="subscript"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color rgb="FF183C1B"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>volwt</t>
@@ -906,9 +906,9 @@
       <rPr>
         <b/>
         <vertAlign val="subscript"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color rgb="FF533001"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>masswt</t>
@@ -1095,108 +1095,106 @@
   </numFmts>
   <fonts count="56" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF533001"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
@@ -1207,272 +1205,265 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="0" tint="-4.9989318521683403E-2"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1" tint="0.14996795556505021"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC44340"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFC44340"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
+      <sz val="10"/>
+      <color rgb="FFCC6600"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color theme="6" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color theme="5" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color theme="1" tint="0.14999847407452621"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
+      <sz val="18"/>
+      <color theme="3" tint="9.9978637043366805E-2"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="14"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <vertAlign val="subscript"/>
+      <sz val="14"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="10"/>
-      <color theme="6" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <sz val="14"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="10"/>
-      <color theme="5" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <vertAlign val="subscript"/>
+      <sz val="10"/>
+      <color rgb="FF183C1B"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <vertAlign val="subscript"/>
+      <sz val="10"/>
+      <color rgb="FF533001"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF404040"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color theme="3" tint="9.9978637043366805E-2"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <vertAlign val="subscript"/>
-      <sz val="16"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="16"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
+      <color theme="10"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <vertAlign val="subscript"/>
-      <sz val="11"/>
-      <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <vertAlign val="subscript"/>
-      <sz val="11"/>
-      <color rgb="FF533001"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF404040"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="16">
@@ -2417,11 +2408,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2441,11 +2431,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2465,11 +2454,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2489,11 +2477,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2513,11 +2500,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2537,11 +2523,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2561,11 +2546,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2585,11 +2569,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2609,11 +2592,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2633,11 +2615,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2657,11 +2638,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2681,11 +2661,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2705,11 +2684,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2729,11 +2707,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2753,11 +2730,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2777,11 +2753,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2801,11 +2776,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2825,11 +2799,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2849,11 +2822,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2873,11 +2845,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2897,11 +2868,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2921,11 +2891,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2945,11 +2914,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2969,11 +2937,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2993,11 +2960,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3017,11 +2983,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3041,11 +3006,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3065,11 +3029,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3089,11 +3052,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3113,11 +3075,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3137,11 +3098,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3161,11 +3121,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3185,11 +3144,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3209,11 +3167,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3233,11 +3190,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3257,11 +3213,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3281,11 +3236,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3305,11 +3259,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.24994659260841701"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="1"/>
-        <scheme val="none"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
@@ -3338,11 +3291,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
@@ -3364,11 +3316,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.24994659260841701"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="1"/>
-        <scheme val="none"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
@@ -3397,11 +3348,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
@@ -3423,11 +3373,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
@@ -3449,11 +3398,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3465,7 +3413,7 @@
     <dxf>
       <font>
         <b/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
         <family val="2"/>
       </font>
@@ -3487,11 +3435,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3511,11 +3458,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3821,7 +3767,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-AU" sz="1400" b="0">
+            <a:rPr lang="en-AU" sz="1200" b="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
@@ -3895,17 +3841,17 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:fld id="{B377A225-5B38-4F4F-8E60-34C9F7D0C552}" type="TxLink">
-            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
             <a:t>Mass of waste from waste volume</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="1000">
+          <a:endParaRPr lang="en-AU" sz="900">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -3977,17 +3923,17 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:fld id="{DE6DD785-2BD4-4778-B848-1DE745244E64}" type="TxLink">
-            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="900" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
             <a:t>Emissions from waste management by greenhouse gas</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="1000" b="1">
+          <a:endParaRPr lang="en-AU" sz="900" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -4116,14 +4062,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑄</m:t>
@@ -4131,7 +4077,7 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑤𝑡</m:t>
@@ -4139,7 +4085,7 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>=</m:t>
@@ -4147,14 +4093,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑉</m:t>
@@ -4162,7 +4108,7 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑤𝑡</m:t>
@@ -4170,13 +4116,13 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>×</m:t>
                     </m:r>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>𝑉𝑇</m:t>
@@ -4184,14 +4130,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑀</m:t>
@@ -4199,7 +4145,7 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑤</m:t>
@@ -4209,7 +4155,7 @@
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -4258,12 +4204,12 @@
             <a:p>
               <a:pPr/>
               <a:r>
-                <a:rPr lang="en-AU" sz="1100" i="0">
+                <a:rPr lang="en-AU" sz="1000" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>𝑄_𝑤𝑡=𝑉_𝑤𝑡×𝑉𝑇𝑀_𝑤</a:t>
               </a:r>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -4329,14 +4275,14 @@
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:sSubPr>
                       <m:e>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝐸</m:t>
@@ -4344,7 +4290,7 @@
                       </m:e>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑔</m:t>
@@ -4352,7 +4298,7 @@
                       </m:sub>
                     </m:sSub>
                     <m:r>
-                      <a:rPr lang="en-AU" sz="1100" i="1">
+                      <a:rPr lang="en-AU" sz="1000" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
                       <m:t>=</m:t>
@@ -4363,14 +4309,14 @@
                         <m:limLoc m:val="subSup"/>
                         <m:supHide m:val="on"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:naryPr>
                       <m:sub>
                         <m:r>
-                          <a:rPr lang="en-AU" sz="1100" i="1">
+                          <a:rPr lang="en-AU" sz="1000" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                           <m:t>𝑡</m:t>
@@ -4384,14 +4330,14 @@
                             <m:limLoc m:val="subSup"/>
                             <m:supHide m:val="on"/>
                             <m:ctrlPr>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
                           </m:naryPr>
                           <m:sub>
                             <m:r>
-                              <a:rPr lang="en-AU" sz="1100" i="1">
+                              <a:rPr lang="en-AU" sz="1000" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                               <m:t>𝑤</m:t>
@@ -4402,7 +4348,7 @@
                             <m:d>
                               <m:dPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
@@ -4411,14 +4357,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑄</m:t>
@@ -4426,7 +4372,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑤𝑡</m:t>
@@ -4434,13 +4380,13 @@
                                   </m:sub>
                                 </m:sSub>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>×</m:t>
                                 </m:r>
                                 <m:r>
-                                  <a:rPr lang="en-AU" sz="1100" i="1">
+                                  <a:rPr lang="en-AU" sz="1000" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                   <m:t>𝐸</m:t>
@@ -4448,14 +4394,14 @@
                                 <m:sSub>
                                   <m:sSubPr>
                                     <m:ctrlPr>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                     </m:ctrlPr>
                                   </m:sSubPr>
                                   <m:e>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝐹</m:t>
@@ -4463,7 +4409,7 @@
                                   </m:e>
                                   <m:sub>
                                     <m:r>
-                                      <a:rPr lang="en-AU" sz="1100" i="1">
+                                      <a:rPr lang="en-AU" sz="1000" i="1">
                                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                       </a:rPr>
                                       <m:t>𝑤𝑡𝑔</m:t>
@@ -4479,7 +4425,7 @@
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -4528,12 +4474,12 @@
             <a:p>
               <a:pPr/>
               <a:r>
-                <a:rPr lang="en-AU" sz="1100" i="0">
+                <a:rPr lang="en-AU" sz="1000" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>𝐸_𝑔=∑2_𝑡▒∑2_𝑤▒(𝑄_𝑤𝑡×𝐸𝐹_𝑤𝑡𝑔 ) </a:t>
               </a:r>
-              <a:endParaRPr lang="en-AU" sz="1100"/>
+              <a:endParaRPr lang="en-AU" sz="1000"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -5295,12 +5241,12 @@
     </a:clrScheme>
     <a:fontScheme name="Custom 1">
       <a:majorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -5511,31 +5457,31 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25" ht="30" customHeight="1">
       <c r="A1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A3" s="74" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A6" s="73" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A7" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A8" s="12" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -5552,7 +5498,7 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:W45"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -5582,7 +5528,7 @@
       <c r="O1" s="50"/>
       <c r="P1" s="50"/>
     </row>
-    <row r="2" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2" s="50"/>
       <c r="D2" s="50"/>
       <c r="E2" s="50"/>
@@ -5599,7 +5545,7 @@
       <c r="P2" s="50"/>
       <c r="Q2" s="51"/>
     </row>
-    <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -5619,13 +5565,13 @@
       <c r="O3" s="52"/>
       <c r="P3" s="52"/>
     </row>
-    <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="40" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -5645,7 +5591,7 @@
       <c r="N5" s="34"/>
       <c r="O5" s="31"/>
     </row>
-    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="53" t="s">
         <v>83</v>
       </c>
@@ -5661,83 +5607,83 @@
       <c r="N6" s="33"/>
       <c r="O6" s="32"/>
     </row>
-    <row r="7" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="str">
         <f>HYPERLINK("#'Input - Solid waste'!A1", "Solid waste")</f>
         <v>Solid waste</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="str">
         <f>HYPERLINK("#'10.1.1-2 Solid waste treatment'!A1", "10.1.1-2 Solid waste treatment")</f>
         <v>10.1.1-2 Solid waste treatment</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O14" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="73" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="str">
         <f>HYPERLINK("#'Constants - Solid Waste'!A1", "Constants - Solid Waste")</f>
         <v>Constants - Solid Waste</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L37" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="38" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="12:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="12:23" x14ac:dyDescent="0.25">
+    <row r="38" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="12:23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="12:23" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="W45" t="s">
         <v>81</v>
       </c>
@@ -5755,7 +5701,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:H87"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="3" width="2.7109375" customWidth="1"/>
@@ -5773,10 +5719,10 @@
         <v>130</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2" s="8"/>
     </row>
-    <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -5788,7 +5734,7 @@
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
-    <row r="4" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
@@ -5802,7 +5748,7 @@
       <c r="G4" s="17"/>
       <c r="H4" s="18"/>
     </row>
-    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="40" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -5814,7 +5760,7 @@
       <c r="G5" s="20"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="16"/>
       <c r="D6" s="15" t="s">
         <v>79</v>
@@ -5824,7 +5770,7 @@
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
     </row>
-    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
@@ -5832,7 +5778,7 @@
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>0</v>
       </c>
@@ -5851,7 +5797,7 @@
       </c>
       <c r="H8" s="16"/>
     </row>
-    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="str">
         <f>HYPERLINK("#'Input - Solid waste'!A1", "Solid waste")</f>
         <v>Solid waste</v>
@@ -5873,7 +5819,7 @@
       </c>
       <c r="H9" s="16"/>
     </row>
-    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="16"/>
       <c r="D10" s="1"/>
       <c r="E10" s="48"/>
@@ -5881,7 +5827,7 @@
       <c r="G10" s="28"/>
       <c r="H10" s="16"/>
     </row>
-    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="16"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -5889,7 +5835,7 @@
       <c r="G11" s="1"/>
       <c r="H11" s="16"/>
     </row>
-    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>44</v>
       </c>
@@ -5908,7 +5854,7 @@
       </c>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="str">
         <f>HYPERLINK("#'10.1.1-2 Solid waste treatment'!A1", "10.1.1-2 Solid waste treatment")</f>
         <v>10.1.1-2 Solid waste treatment</v>
@@ -5930,7 +5876,7 @@
       </c>
       <c r="H13" s="16"/>
     </row>
-    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="16"/>
       <c r="D14" s="1"/>
       <c r="E14" s="37"/>
@@ -5938,7 +5884,7 @@
       <c r="G14" s="1"/>
       <c r="H14" s="16"/>
     </row>
-    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="16"/>
       <c r="D15" s="1"/>
       <c r="E15" s="37"/>
@@ -5946,7 +5892,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="73" t="s">
         <v>1</v>
       </c>
@@ -5957,7 +5903,7 @@
       <c r="G16" s="1"/>
       <c r="H16" s="16"/>
     </row>
-    <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="str">
         <f>HYPERLINK("#'Constants - Solid Waste'!A1", "Constants - Solid Waste")</f>
         <v>Constants - Solid Waste</v>
@@ -5969,7 +5915,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="16"/>
     </row>
-    <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -5981,7 +5927,7 @@
       <c r="G18" s="1"/>
       <c r="H18" s="16"/>
     </row>
-    <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="16"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -5989,7 +5935,7 @@
       <c r="G19" s="1"/>
       <c r="H19" s="16"/>
     </row>
-    <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="16"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -5997,7 +5943,7 @@
       <c r="G20" s="1"/>
       <c r="H20" s="16"/>
     </row>
-    <row r="21" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="16"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -6005,7 +5951,7 @@
       <c r="G21" s="1"/>
       <c r="H21" s="16"/>
     </row>
-    <row r="22" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="16"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -6013,7 +5959,7 @@
       <c r="G22" s="1"/>
       <c r="H22" s="16"/>
     </row>
-    <row r="23" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="16"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -6021,7 +5967,7 @@
       <c r="G23" s="1"/>
       <c r="H23" s="16"/>
     </row>
-    <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="16"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -6029,7 +5975,7 @@
       <c r="G24" s="1"/>
       <c r="H24" s="16"/>
     </row>
-    <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="16"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -6037,7 +5983,7 @@
       <c r="G25" s="1"/>
       <c r="H25" s="16"/>
     </row>
-    <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="16"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -6045,7 +5991,7 @@
       <c r="G26" s="1"/>
       <c r="H26" s="16"/>
     </row>
-    <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="16"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -6053,7 +5999,7 @@
       <c r="G27" s="1"/>
       <c r="H27" s="16"/>
     </row>
-    <row r="28" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="16"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -6061,7 +6007,7 @@
       <c r="G28" s="1"/>
       <c r="H28" s="16"/>
     </row>
-    <row r="29" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="16"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -6069,7 +6015,7 @@
       <c r="G29" s="1"/>
       <c r="H29" s="16"/>
     </row>
-    <row r="30" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="16"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -6077,7 +6023,7 @@
       <c r="G30" s="1"/>
       <c r="H30" s="16"/>
     </row>
-    <row r="31" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" s="16"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -6085,7 +6031,7 @@
       <c r="G31" s="1"/>
       <c r="H31" s="16"/>
     </row>
-    <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="16"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -6093,7 +6039,7 @@
       <c r="G32" s="1"/>
       <c r="H32" s="16"/>
     </row>
-    <row r="33" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33" s="16"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -6101,7 +6047,7 @@
       <c r="G33" s="1"/>
       <c r="H33" s="16"/>
     </row>
-    <row r="34" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34" s="16"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -6109,7 +6055,7 @@
       <c r="G34" s="1"/>
       <c r="H34" s="16"/>
     </row>
-    <row r="35" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="16"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -6117,7 +6063,7 @@
       <c r="G35" s="1"/>
       <c r="H35" s="16"/>
     </row>
-    <row r="36" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C36" s="16"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -6125,7 +6071,7 @@
       <c r="G36" s="1"/>
       <c r="H36" s="16"/>
     </row>
-    <row r="37" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="16"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -6133,7 +6079,7 @@
       <c r="G37" s="1"/>
       <c r="H37" s="16"/>
     </row>
-    <row r="38" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="16"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -6141,7 +6087,7 @@
       <c r="G38" s="1"/>
       <c r="H38" s="16"/>
     </row>
-    <row r="39" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C39" s="16"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -6149,7 +6095,7 @@
       <c r="G39" s="1"/>
       <c r="H39" s="16"/>
     </row>
-    <row r="40" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="16"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
@@ -6157,7 +6103,7 @@
       <c r="G40" s="1"/>
       <c r="H40" s="16"/>
     </row>
-    <row r="41" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C41" s="16"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -6165,7 +6111,7 @@
       <c r="G41" s="1"/>
       <c r="H41" s="16"/>
     </row>
-    <row r="42" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C42" s="16"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -6173,7 +6119,7 @@
       <c r="G42" s="1"/>
       <c r="H42" s="16"/>
     </row>
-    <row r="43" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" s="16"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -6181,7 +6127,7 @@
       <c r="G43" s="1"/>
       <c r="H43" s="16"/>
     </row>
-    <row r="44" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C44" s="16"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -6189,7 +6135,7 @@
       <c r="G44" s="1"/>
       <c r="H44" s="16"/>
     </row>
-    <row r="45" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" s="16"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -6197,7 +6143,7 @@
       <c r="G45" s="1"/>
       <c r="H45" s="16"/>
     </row>
-    <row r="46" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46" s="16"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -6205,7 +6151,7 @@
       <c r="G46" s="1"/>
       <c r="H46" s="16"/>
     </row>
-    <row r="47" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C47" s="16"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -6213,7 +6159,7 @@
       <c r="G47" s="1"/>
       <c r="H47" s="16"/>
     </row>
-    <row r="48" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C48" s="16"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -6221,7 +6167,7 @@
       <c r="G48" s="1"/>
       <c r="H48" s="16"/>
     </row>
-    <row r="49" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C49" s="16"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -6229,7 +6175,7 @@
       <c r="G49" s="1"/>
       <c r="H49" s="16"/>
     </row>
-    <row r="50" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C50" s="16"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -6237,7 +6183,7 @@
       <c r="G50" s="1"/>
       <c r="H50" s="16"/>
     </row>
-    <row r="51" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C51" s="16"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -6245,7 +6191,7 @@
       <c r="G51" s="1"/>
       <c r="H51" s="16"/>
     </row>
-    <row r="52" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C52" s="16"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -6253,7 +6199,7 @@
       <c r="G52" s="1"/>
       <c r="H52" s="16"/>
     </row>
-    <row r="53" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C53" s="16"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -6261,7 +6207,7 @@
       <c r="G53" s="1"/>
       <c r="H53" s="16"/>
     </row>
-    <row r="54" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C54" s="16"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -6269,7 +6215,7 @@
       <c r="G54" s="1"/>
       <c r="H54" s="16"/>
     </row>
-    <row r="55" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C55" s="16"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -6277,7 +6223,7 @@
       <c r="G55" s="1"/>
       <c r="H55" s="16"/>
     </row>
-    <row r="56" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C56" s="16"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -6285,7 +6231,7 @@
       <c r="G56" s="1"/>
       <c r="H56" s="16"/>
     </row>
-    <row r="57" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C57" s="16"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -6293,7 +6239,7 @@
       <c r="G57" s="1"/>
       <c r="H57" s="16"/>
     </row>
-    <row r="58" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C58" s="16"/>
       <c r="D58" s="1"/>
       <c r="E58" s="22"/>
@@ -6301,7 +6247,7 @@
       <c r="G58" s="16"/>
       <c r="H58" s="16"/>
     </row>
-    <row r="59" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C59" s="16"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -6309,7 +6255,7 @@
       <c r="G59" s="1"/>
       <c r="H59" s="16"/>
     </row>
-    <row r="60" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C60" s="16"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -6317,7 +6263,7 @@
       <c r="G60" s="1"/>
       <c r="H60" s="16"/>
     </row>
-    <row r="61" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C61" s="16"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -6325,7 +6271,7 @@
       <c r="G61" s="1"/>
       <c r="H61" s="16"/>
     </row>
-    <row r="62" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C62" s="16"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
@@ -6333,7 +6279,7 @@
       <c r="G62" s="1"/>
       <c r="H62" s="16"/>
     </row>
-    <row r="63" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C63" s="16"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -6341,7 +6287,7 @@
       <c r="G63" s="1"/>
       <c r="H63" s="16"/>
     </row>
-    <row r="64" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C64" s="16"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -6349,7 +6295,7 @@
       <c r="G64" s="1"/>
       <c r="H64" s="16"/>
     </row>
-    <row r="65" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C65" s="16"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -6357,7 +6303,7 @@
       <c r="G65" s="1"/>
       <c r="H65" s="16"/>
     </row>
-    <row r="66" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C66" s="16"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
@@ -6365,7 +6311,7 @@
       <c r="G66" s="1"/>
       <c r="H66" s="16"/>
     </row>
-    <row r="67" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C67" s="16"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
@@ -6373,7 +6319,7 @@
       <c r="G67" s="1"/>
       <c r="H67" s="16"/>
     </row>
-    <row r="68" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C68" s="16"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
@@ -6381,7 +6327,7 @@
       <c r="G68" s="1"/>
       <c r="H68" s="16"/>
     </row>
-    <row r="69" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C69" s="16"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -6389,7 +6335,7 @@
       <c r="G69" s="1"/>
       <c r="H69" s="16"/>
     </row>
-    <row r="70" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C70" s="16"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
@@ -6397,7 +6343,7 @@
       <c r="G70" s="1"/>
       <c r="H70" s="16"/>
     </row>
-    <row r="71" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C71" s="16"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
@@ -6405,7 +6351,7 @@
       <c r="G71" s="1"/>
       <c r="H71" s="16"/>
     </row>
-    <row r="72" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C72" s="16"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
@@ -6413,7 +6359,7 @@
       <c r="G72" s="1"/>
       <c r="H72" s="16"/>
     </row>
-    <row r="73" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C73" s="16"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
@@ -6421,7 +6367,7 @@
       <c r="G73" s="1"/>
       <c r="H73" s="16"/>
     </row>
-    <row r="74" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C74" s="16"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -6429,7 +6375,7 @@
       <c r="G74" s="1"/>
       <c r="H74" s="16"/>
     </row>
-    <row r="75" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C75" s="16"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -6437,7 +6383,7 @@
       <c r="G75" s="1"/>
       <c r="H75" s="16"/>
     </row>
-    <row r="76" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C76" s="16"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
@@ -6445,7 +6391,7 @@
       <c r="G76" s="1"/>
       <c r="H76" s="16"/>
     </row>
-    <row r="77" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C77" s="16"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
@@ -6453,7 +6399,7 @@
       <c r="G77" s="1"/>
       <c r="H77" s="16"/>
     </row>
-    <row r="78" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C78" s="16"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
@@ -6461,7 +6407,7 @@
       <c r="G78" s="1"/>
       <c r="H78" s="16"/>
     </row>
-    <row r="79" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C79" s="16"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
@@ -6469,7 +6415,7 @@
       <c r="G79" s="1"/>
       <c r="H79" s="16"/>
     </row>
-    <row r="80" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C80" s="16"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
@@ -6477,7 +6423,7 @@
       <c r="G80" s="1"/>
       <c r="H80" s="16"/>
     </row>
-    <row r="81" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C81" s="16"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
@@ -6485,7 +6431,7 @@
       <c r="G81" s="1"/>
       <c r="H81" s="16"/>
     </row>
-    <row r="82" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C82" s="16"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
@@ -6493,7 +6439,7 @@
       <c r="G82" s="1"/>
       <c r="H82" s="16"/>
     </row>
-    <row r="83" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C83" s="16"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
@@ -6501,7 +6447,7 @@
       <c r="G83" s="1"/>
       <c r="H83" s="16"/>
     </row>
-    <row r="84" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C84" s="16"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
@@ -6509,7 +6455,7 @@
       <c r="G84" s="1"/>
       <c r="H84" s="16"/>
     </row>
-    <row r="85" spans="3:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C85" s="16"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
@@ -6517,7 +6463,7 @@
       <c r="G85" s="1"/>
       <c r="H85" s="16"/>
     </row>
-    <row r="86" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C86" s="16"/>
       <c r="D86" s="16"/>
       <c r="E86" s="16"/>
@@ -6525,7 +6471,7 @@
       <c r="G86" s="16"/>
       <c r="H86" s="16"/>
     </row>
-    <row r="87" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C87" s="16"/>
       <c r="D87" s="16"/>
       <c r="E87" s="16"/>
@@ -6544,7 +6490,7 @@
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:L385"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -6567,10 +6513,10 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="8" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -6584,13 +6530,13 @@
       <c r="I3" s="11"/>
       <c r="J3" s="11"/>
     </row>
-    <row r="4" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -6599,19 +6545,19 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" s="55" t="s">
         <v>86</v>
       </c>
       <c r="E7" s="56"/>
     </row>
-    <row r="8" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="39" t="str">
         <f>HYPERLINK("#'Input - Solid waste'!A1", "Solid waste")</f>
         <v>Solid waste</v>
@@ -6635,7 +6581,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="75" t="s">
         <v>147</v>
       </c>
@@ -6655,7 +6601,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="75" t="s">
         <v>148</v>
       </c>
@@ -6675,7 +6621,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>44</v>
       </c>
@@ -6698,7 +6644,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="str">
         <f>HYPERLINK("#'10.1.1-2 Solid waste treatment'!A1", "10.1.1-2 Solid waste treatment")</f>
         <v>10.1.1-2 Solid waste treatment</v>
@@ -6722,7 +6668,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="75" t="s">
         <v>134</v>
       </c>
@@ -6742,7 +6688,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="75" t="s">
         <v>135</v>
       </c>
@@ -6762,7 +6708,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="73" t="s">
         <v>1</v>
       </c>
@@ -6785,7 +6731,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="str">
         <f>HYPERLINK("#'Constants - Solid Waste'!A1", "Constants - Solid Waste")</f>
         <v>Constants - Solid Waste</v>
@@ -6809,7 +6755,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -6833,7 +6779,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="75" t="s">
         <v>137</v>
       </c>
@@ -6853,7 +6799,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="75" t="s">
         <v>138</v>
       </c>
@@ -6873,7 +6819,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="75" t="s">
         <v>139</v>
       </c>
@@ -6893,7 +6839,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="75" t="s">
         <v>140</v>
       </c>
@@ -6913,7 +6859,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="75" t="s">
         <v>141</v>
       </c>
@@ -6933,7 +6879,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D24" s="75" t="s">
         <v>142</v>
       </c>
@@ -6953,7 +6899,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="75" t="s">
         <v>143</v>
       </c>
@@ -6973,7 +6919,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="75" t="s">
         <v>155</v>
       </c>
@@ -6993,7 +6939,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="75" t="s">
         <v>156</v>
       </c>
@@ -7013,7 +6959,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="75" t="s">
         <v>157</v>
       </c>
@@ -7033,7 +6979,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="75" t="s">
         <v>158</v>
       </c>
@@ -7054,7 +7000,7 @@
       </c>
       <c r="K29" s="44"/>
     </row>
-    <row r="30" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="75" t="s">
         <v>159</v>
       </c>
@@ -7075,7 +7021,7 @@
       </c>
       <c r="K30" s="44"/>
     </row>
-    <row r="31" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="75" t="s">
         <v>160</v>
       </c>
@@ -7096,7 +7042,7 @@
       </c>
       <c r="K31" s="44"/>
     </row>
-    <row r="32" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D32" s="75" t="s">
         <v>158</v>
       </c>
@@ -7117,27 +7063,27 @@
       </c>
       <c r="K32" s="44"/>
     </row>
-    <row r="33" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K33" s="44"/>
     </row>
-    <row r="34" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="K34" s="44"/>
     </row>
-    <row r="35" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L36" s="44"/>
     </row>
-    <row r="37" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L37" s="44"/>
     </row>
-    <row r="38" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="43"/>
     </row>
-    <row r="39" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C39" s="43"/>
       <c r="J39" s="43"/>
     </row>
-    <row r="40" spans="1:12" s="44" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -7148,7 +7094,7 @@
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
     </row>
-    <row r="41" spans="1:12" s="44" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" s="44" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -7162,137 +7108,137 @@
         <v>84</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D73" s="61"/>
     </row>
-    <row r="74" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D75" s="61"/>
     </row>
-    <row r="76" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D76" s="61"/>
     </row>
-    <row r="77" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" spans="4:4" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D385" s="35"/>
     </row>
   </sheetData>
@@ -7424,7 +7370,7 @@
     <tabColor rgb="FF008000"/>
   </sheetPr>
   <dimension ref="A1:L342"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -7442,10 +7388,10 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="8" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -7463,13 +7409,13 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
-    <row r="4" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -7479,13 +7425,13 @@
         <v>Mass of waste from waste volume</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="4" t="str" cm="1">
         <f t="array" ref="D6">WasteSolid_Equations.VEERG_10_1_1_1__2_MassOfWasteFromVolume_Source()</f>
         <v>VEERG 2026: 10.1.1.1, Equation (2)</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" s="10" t="s">
         <v>9</v>
       </c>
@@ -7494,18 +7440,18 @@
         <v>=WasteSolid_Equations.VEERG_10_1_1_1__2_MassOfWasteFromVolume</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="str">
         <f>HYPERLINK("#'Input - Solid waste'!A1", "Solid waste")</f>
         <v>Solid waste</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="27" t="s">
         <v>12</v>
       </c>
@@ -7514,7 +7460,7 @@
         <v>Q_wt</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="27" t="s">
         <v>4</v>
       </c>
@@ -7523,12 +7469,12 @@
         <v>t</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="63" t="str">
         <f>HYPERLINK("#'10.1.1-2 Solid waste treatment'!A1", "10.1.1-2 Solid waste treatment")</f>
         <v>10.1.1-2 Solid waste treatment</v>
@@ -7557,7 +7503,7 @@
         <v>Table_V_w_t_offsite</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="45" t="str">
         <v>VTM_w</v>
       </c>
@@ -7580,7 +7526,7 @@
         <v>Table_V_w_t_offsite</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="45" t="str">
         <v>w</v>
       </c>
@@ -7603,7 +7549,7 @@
         <v>Table_V_w_t_offsite</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="73" t="s">
         <v>1</v>
       </c>
@@ -7629,13 +7575,13 @@
         <v>Table_V_w_t_offsite</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="str">
         <f>HYPERLINK("#'Constants - Solid Waste'!A1", "Constants - Solid Waste")</f>
         <v>Constants - Solid Waste</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -7644,12 +7590,12 @@
         <v>116</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="66" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="62" t="s">
         <v>93</v>
       </c>
@@ -7667,7 +7613,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="45" t="str" cm="1">
         <f t="array" ref="D21:D54">Table_SourceData_WasteSolid_WasteTreatmentEFs[Treatment type t]</f>
         <v>Landfill</v>
@@ -7690,7 +7636,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -7711,7 +7657,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -7732,7 +7678,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D24" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -7753,7 +7699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -7774,7 +7720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -7795,7 +7741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -7816,7 +7762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -7837,7 +7783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -7858,7 +7804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -7879,7 +7825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -7900,7 +7846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D32" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -7918,7 +7864,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="33" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -7939,7 +7885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D34" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -7960,7 +7906,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -7981,7 +7927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D36" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -8002,7 +7948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -8023,7 +7969,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="38" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -8044,7 +7990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D39" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -8065,7 +8011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D40" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -8086,7 +8032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -8107,7 +8053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -8128,7 +8074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="45" t="str">
         <v>Composting</v>
       </c>
@@ -8146,7 +8092,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="44" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="45" t="str">
         <v>Composting</v>
       </c>
@@ -8167,7 +8113,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="45" t="str">
         <v>Composting</v>
       </c>
@@ -8188,7 +8134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" s="45" t="str">
         <v>Composting</v>
       </c>
@@ -8209,7 +8155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="45" t="str">
         <v>Composting</v>
       </c>
@@ -8230,7 +8176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D48" s="45" t="str">
         <v>Composting</v>
       </c>
@@ -8251,7 +8197,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="49" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D49" s="45" t="str">
         <v>Anaerobic digestion</v>
       </c>
@@ -8269,7 +8215,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="50" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D50" s="45" t="str">
         <v>Anaerobic digestion</v>
       </c>
@@ -8290,7 +8236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D51" s="45" t="str">
         <v>Anaerobic digestion</v>
       </c>
@@ -8311,7 +8257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D52" s="45" t="str">
         <v>Anaerobic digestion</v>
       </c>
@@ -8332,7 +8278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D53" s="45" t="str">
         <v>Anaerobic digestion</v>
       </c>
@@ -8353,7 +8299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D54" s="45" t="str">
         <v>Anaerobic digestion</v>
       </c>
@@ -8374,18 +8320,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D56" s="65" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="57" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D57" s="66" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="58" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D58" s="62" t="s">
         <v>93</v>
       </c>
@@ -8403,7 +8349,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="59" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D59" s="45" t="str" cm="1">
         <f t="array" ref="D59:D92">Table_SourceData_WasteSolid_WasteTreatmentEFs[Treatment type t]</f>
         <v>Landfill</v>
@@ -8426,7 +8372,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D60" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -8447,7 +8393,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="61" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D61" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -8468,7 +8414,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D62" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -8489,7 +8435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D63" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -8510,7 +8456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D64" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -8531,7 +8477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D65" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -8552,7 +8498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D66" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -8573,7 +8519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D67" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -8594,7 +8540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D68" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -8615,7 +8561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D69" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -8636,7 +8582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D70" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -8654,7 +8600,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="71" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D71" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -8675,7 +8621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D72" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -8696,7 +8642,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D73" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -8717,7 +8663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D74" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -8738,7 +8684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D75" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -8759,7 +8705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D76" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -8780,7 +8726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D77" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -8801,7 +8747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D78" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -8822,7 +8768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D79" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -8843,7 +8789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D80" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -8864,7 +8810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D81" s="45" t="str">
         <v>Composting</v>
       </c>
@@ -8882,7 +8828,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="82" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D82" s="45" t="str">
         <v>Composting</v>
       </c>
@@ -8903,7 +8849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D83" s="45" t="str">
         <v>Composting</v>
       </c>
@@ -8924,7 +8870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D84" s="45" t="str">
         <v>Composting</v>
       </c>
@@ -8945,7 +8891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D85" s="45" t="str">
         <v>Composting</v>
       </c>
@@ -8966,7 +8912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D86" s="45" t="str">
         <v>Composting</v>
       </c>
@@ -8987,7 +8933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D87" s="45" t="str">
         <v>Anaerobic digestion</v>
       </c>
@@ -9005,7 +8951,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="88" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D88" s="45" t="str">
         <v>Anaerobic digestion</v>
       </c>
@@ -9026,7 +8972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D89" s="45" t="str">
         <v>Anaerobic digestion</v>
       </c>
@@ -9047,7 +8993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D90" s="45" t="str">
         <v>Anaerobic digestion</v>
       </c>
@@ -9068,7 +9014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D91" s="45" t="str">
         <v>Anaerobic digestion</v>
       </c>
@@ -9089,7 +9035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D92" s="45" t="str">
         <v>Anaerobic digestion</v>
       </c>
@@ -9110,9 +9056,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C95" s="58"/>
       <c r="D95" s="58"/>
       <c r="E95" s="58"/>
@@ -9124,25 +9070,25 @@
       <c r="K95" s="58"/>
       <c r="L95" s="58"/>
     </row>
-    <row r="96" spans="3:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D96" s="5" t="str" cm="1">
         <f t="array" ref="D96">WasteSolid_Equations.VEERG_10_1_1_1__1_EmissionsFromWasteManagement_Title()</f>
         <v>Emissions from waste management by greenhouse gas</v>
       </c>
     </row>
-    <row r="97" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D97" s="4" t="str" cm="1">
         <f t="array" ref="D97">WasteSolid_Equations.VEERG_10_1_1_1__1_EmissionsFromWasteManagement_Source()</f>
         <v>VEERG 2026: 10.1.1.1, Equation (1)</v>
       </c>
     </row>
-    <row r="98" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D98" s="29" t="str" cm="1">
         <f t="array" ref="D98">WasteSolid_Equations.VEERG_10_1_1_1__1_EmissionsFromWasteManagement_Variation()</f>
         <v>VARIATION ON SOURCE: Added Q_volwt and Q_masswt variables to clearly track input or calculated Q values</v>
       </c>
     </row>
-    <row r="99" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D99" s="10" t="s">
         <v>9</v>
       </c>
@@ -9151,9 +9097,9 @@
         <v>=WasteSolid_Equations.VEERG_10_1_1_1__1_EmissionsFromWasteManagement</v>
       </c>
     </row>
-    <row r="100" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D102" s="27" t="s">
         <v>12</v>
       </c>
@@ -9162,7 +9108,7 @@
         <v>E_g</v>
       </c>
     </row>
-    <row r="103" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D103" s="27" t="s">
         <v>4</v>
       </c>
@@ -9171,8 +9117,8 @@
         <v>t CO2e</v>
       </c>
     </row>
-    <row r="104" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D105" s="45" t="str" cm="1">
         <f t="array" ref="D105:E111">_xlfn.CHOOSECOLS(WasteSolid_Equations.VEERG_10_1_1_1__1_EmissionsFromWasteManagement_Arguments(),1,2)</f>
         <v>Q_wt</v>
@@ -9190,7 +9136,7 @@
         <v>Sum of Q_volwt and Q_masswt</v>
       </c>
     </row>
-    <row r="106" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D106" s="45" t="str">
         <v>EF_wtg</v>
       </c>
@@ -9206,7 +9152,7 @@
         <v>Constant</v>
       </c>
     </row>
-    <row r="107" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D107" s="45" t="str">
         <v>w</v>
       </c>
@@ -9222,7 +9168,7 @@
         <v>Input</v>
       </c>
     </row>
-    <row r="108" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D108" s="45" t="str">
         <v>t</v>
       </c>
@@ -9238,7 +9184,7 @@
         <v>Input</v>
       </c>
     </row>
-    <row r="109" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D109" s="45" t="str">
         <v>g</v>
       </c>
@@ -9254,7 +9200,7 @@
         <v>Input</v>
       </c>
     </row>
-    <row r="110" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D110" s="45" t="str">
         <v>Q_volwt</v>
       </c>
@@ -9270,7 +9216,7 @@
         <v>Calculated from 10.1.1.1 (2)</v>
       </c>
     </row>
-    <row r="111" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D111" s="45" t="str">
         <v>Q_masswt</v>
       </c>
@@ -9286,18 +9232,18 @@
         <v>Input</v>
       </c>
     </row>
-    <row r="112" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D113" s="65" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="114" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D114" s="66" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="115" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D115" s="62" t="s">
         <v>93</v>
       </c>
@@ -9321,7 +9267,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="116" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D116" s="45" t="str" cm="1">
         <f t="array" ref="D116:D149">Table_SourceData_WasteSolid_WasteTreatmentEFs[Treatment type t]</f>
         <v>Landfill</v>
@@ -9352,7 +9298,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="117" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D117" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -9381,7 +9327,7 @@
         <v>179.85</v>
       </c>
     </row>
-    <row r="118" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D118" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -9410,7 +9356,7 @@
         <v>99.2</v>
       </c>
     </row>
-    <row r="119" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D119" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -9439,7 +9385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D120" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -9468,7 +9414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D121" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -9497,7 +9443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D122" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -9526,7 +9472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D123" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -9555,7 +9501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D124" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -9584,7 +9530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D125" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -9613,7 +9559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D126" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -9642,7 +9588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D127" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -9670,7 +9616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D128" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -9696,7 +9642,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="129" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D129" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -9722,7 +9668,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="130" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D130" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -9748,7 +9694,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="131" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D131" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -9774,7 +9720,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="132" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D132" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -9803,7 +9749,7 @@
         <v>0.92104999999999992</v>
       </c>
     </row>
-    <row r="133" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D133" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -9832,7 +9778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D134" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -9861,7 +9807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D135" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -9890,7 +9836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D136" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -9919,7 +9865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D137" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -9948,7 +9894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D138" s="45" t="str">
         <v>Composting</v>
       </c>
@@ -9976,7 +9922,7 @@
         <v>1.357</v>
       </c>
     </row>
-    <row r="139" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D139" s="45" t="str">
         <v>Composting</v>
       </c>
@@ -10002,7 +9948,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="140" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D140" s="45" t="str">
         <v>Composting</v>
       </c>
@@ -10028,7 +9974,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="141" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D141" s="45" t="str">
         <v>Composting</v>
       </c>
@@ -10054,7 +10000,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="142" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D142" s="45" t="str">
         <v>Composting</v>
       </c>
@@ -10080,7 +10026,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="143" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D143" s="45" t="str">
         <v>Composting</v>
       </c>
@@ -10106,7 +10052,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="144" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D144" s="45" t="str">
         <v>Anaerobic digestion</v>
       </c>
@@ -10134,7 +10080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D145" s="45" t="str">
         <v>Anaerobic digestion</v>
       </c>
@@ -10160,7 +10106,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="146" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D146" s="45" t="str">
         <v>Anaerobic digestion</v>
       </c>
@@ -10186,7 +10132,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="147" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D147" s="45" t="str">
         <v>Anaerobic digestion</v>
       </c>
@@ -10212,7 +10158,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="148" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D148" s="45" t="str">
         <v>Anaerobic digestion</v>
       </c>
@@ -10238,7 +10184,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="149" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D149" s="45" t="str">
         <v>Anaerobic digestion</v>
       </c>
@@ -10264,8 +10210,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="150" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D151" s="57" t="s">
         <v>118</v>
       </c>
@@ -10278,19 +10224,19 @@
         <v>t CO2e</v>
       </c>
     </row>
-    <row r="152" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D154" s="65" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="155" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D155" s="66" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="156" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D156" s="62" t="s">
         <v>93</v>
       </c>
@@ -10314,7 +10260,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="157" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D157" s="45" t="str" cm="1">
         <f t="array" ref="D157:D190">Table_SourceData_WasteSolid_WasteTreatmentEFs[Treatment type t]</f>
         <v>Landfill</v>
@@ -10345,7 +10291,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="158" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D158" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -10374,7 +10320,7 @@
         <v>179.85</v>
       </c>
     </row>
-    <row r="159" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D159" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -10403,7 +10349,7 @@
         <v>99.2</v>
       </c>
     </row>
-    <row r="160" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D160" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -10432,7 +10378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D161" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -10461,7 +10407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D162" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -10490,7 +10436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D163" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -10519,7 +10465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D164" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -10548,7 +10494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D165" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -10577,7 +10523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D166" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -10606,7 +10552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D167" s="45" t="str">
         <v>Landfill</v>
       </c>
@@ -10635,7 +10581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D168" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -10663,7 +10609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D169" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -10689,7 +10635,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="170" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D170" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -10715,7 +10661,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="171" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D171" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -10741,7 +10687,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="172" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D172" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -10767,7 +10713,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="173" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D173" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -10796,7 +10742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D174" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -10825,7 +10771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D175" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -10854,7 +10800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D176" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -10883,7 +10829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D177" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -10912,7 +10858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D178" s="45" t="str">
         <v>Incineration</v>
       </c>
@@ -10941,7 +10887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D179" s="45" t="str">
         <v>Composting</v>
       </c>
@@ -10969,7 +10915,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="180" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D180" s="45" t="str">
         <v>Composting</v>
       </c>
@@ -10995,7 +10941,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="181" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D181" s="45" t="str">
         <v>Composting</v>
       </c>
@@ -11021,7 +10967,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="182" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D182" s="45" t="str">
         <v>Composting</v>
       </c>
@@ -11047,7 +10993,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="183" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D183" s="45" t="str">
         <v>Composting</v>
       </c>
@@ -11073,7 +11019,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="184" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D184" s="45" t="str">
         <v>Composting</v>
       </c>
@@ -11099,7 +11045,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="185" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D185" s="45" t="str">
         <v>Anaerobic digestion</v>
       </c>
@@ -11127,7 +11073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D186" s="45" t="str">
         <v>Anaerobic digestion</v>
       </c>
@@ -11153,7 +11099,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="187" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D187" s="45" t="str">
         <v>Anaerobic digestion</v>
       </c>
@@ -11179,7 +11125,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="188" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D188" s="45" t="str">
         <v>Anaerobic digestion</v>
       </c>
@@ -11205,7 +11151,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="189" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D189" s="45" t="str">
         <v>Anaerobic digestion</v>
       </c>
@@ -11231,7 +11177,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="190" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D190" s="45" t="str">
         <v>Anaerobic digestion</v>
       </c>
@@ -11257,8 +11203,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="191" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="4:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" spans="4:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D192" s="57" t="s">
         <v>118</v>
       </c>
@@ -11271,89 +11217,89 @@
         <v>t CO2e</v>
       </c>
     </row>
-    <row r="193" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="193" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" spans="8:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="H341" s="16"/>
     </row>
-    <row r="342" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="342" spans="8:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="H342" s="16"/>
     </row>
   </sheetData>
@@ -11372,7 +11318,7 @@
     <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:AI165"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -11399,13 +11345,13 @@
       <c r="AH1"/>
       <c r="AI1"/>
     </row>
-    <row r="2" spans="1:35" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" s="8" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
       <c r="AG2"/>
       <c r="AH2"/>
       <c r="AI2"/>
     </row>
-    <row r="3" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -11441,13 +11387,13 @@
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
     </row>
-    <row r="4" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -11457,19 +11403,19 @@
         <v>Emission factors for wastes disposed of at different treatment facilities</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="4" t="str" cm="1">
         <f t="array" ref="D6">WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Source()</f>
         <v>VEERG 2026: Table A.4.1.1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" s="29" t="str" cm="1">
         <f t="array" ref="D7:D13">WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Variation()</f>
         <v>VARIATION ON SOURCE:</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>0</v>
       </c>
@@ -11477,7 +11423,7 @@
         <v>Fixed typo 'paper and carboard' to 'paper and cardboard'</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="str">
         <f>HYPERLINK("#'Input - Solid waste'!A1", "Solid waste")</f>
         <v>Solid waste</v>
@@ -11486,17 +11432,17 @@
         <v>Fixed typo 'prunnings' to 'prunings'</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="29" t="str">
         <v>Added EF source column with specific references</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="29" t="str">
         <v>Added sub-categories for 'Incineration: Food waste, green waste, wood, sludge' in order to use volume to mass conversion factor values</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>44</v>
       </c>
@@ -11504,7 +11450,7 @@
         <v>Added sub-categories for 'Composting: All organic waste' in order to use volume to mass conversion factor values</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="str">
         <f>HYPERLINK("#'10.1.1-2 Solid waste treatment'!A1", "10.1.1-2 Solid waste treatment")</f>
         <v>10.1.1-2 Solid waste treatment</v>
@@ -11513,13 +11459,13 @@
         <v>Added sub-categories for 'Anaerobic digestion: All organic waste' in order to use volume to mass conversion factor values</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="1" t="str" cm="1">
         <f t="array" ref="D14">WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Variable()</f>
         <v>EFwt</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="28" t="str" cm="1">
         <f t="array" ref="D15">WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Unit()</f>
         <v>t CO2e / t</v>
@@ -11537,7 +11483,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="73" t="s">
         <v>1</v>
       </c>
@@ -11566,7 +11512,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="54" t="str">
         <f>HYPERLINK("#'Constants - Solid Waste'!A1", "Constants - Solid Waste")</f>
         <v>Constants - Solid Waste</v>
@@ -11604,7 +11550,7 @@
         <v>Food waste (including animal carcasses, spoiled animal feed or crop)</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -11642,7 +11588,7 @@
         <v>Green waste (including crop residues or prunings)</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="1" t="str" cm="1">
         <f t="array" ref="D19">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Landfill</v>
@@ -11676,7 +11622,7 @@
         <v>Wood</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="str" cm="1">
         <f t="array" ref="D20">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Landfill</v>
@@ -11710,7 +11656,7 @@
         <v>Sludge</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="1" t="str" cm="1">
         <f t="array" ref="D21">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Landfill</v>
@@ -11744,7 +11690,7 @@
         <v>Paper and cardboard</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="1" t="str" cm="1">
         <f t="array" ref="D22">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Landfill</v>
@@ -11770,7 +11716,7 @@
         <v>Textiles</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="1" t="str" cm="1">
         <f t="array" ref="D23">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Landfill</v>
@@ -11796,7 +11742,7 @@
         <v>Rubber and leather</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D24" s="1" t="str" cm="1">
         <f t="array" ref="D24">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Landfill</v>
@@ -11822,7 +11768,7 @@
         <v>Inert waste (including concrete, metal, plastic or glass)</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="1" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Landfill</v>
@@ -11848,7 +11794,7 @@
         <v>Municipal solid waste</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="1" t="str" cm="1">
         <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Landfill</v>
@@ -11874,7 +11820,7 @@
         <v>Commercial and industrial waste</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="1" t="str" cm="1">
         <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Landfill</v>
@@ -11896,7 +11842,7 @@
         <v>Construction and demolition waste</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="1" t="str" cm="1">
         <f t="array" ref="D28">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Incineration</v>
@@ -11914,7 +11860,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="1" t="str" cm="1">
         <f t="array" ref="D29">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Incineration</v>
@@ -11932,7 +11878,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="1" t="str" cm="1">
         <f t="array" ref="D30">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Incineration</v>
@@ -11950,7 +11896,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="1" t="str" cm="1">
         <f t="array" ref="D31">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Incineration</v>
@@ -11968,7 +11914,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D32" s="1" t="str" cm="1">
         <f t="array" ref="D32">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Incineration</v>
@@ -11986,7 +11932,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" s="1" t="str" cm="1">
         <f t="array" ref="D33">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Incineration</v>
@@ -12004,7 +11950,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D34" s="1" t="str" cm="1">
         <f t="array" ref="D34">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Incineration</v>
@@ -12022,7 +11968,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="1" t="str" cm="1">
         <f t="array" ref="D35">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Incineration</v>
@@ -12040,7 +11986,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D36" s="1" t="str" cm="1">
         <f t="array" ref="D36">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Incineration</v>
@@ -12058,7 +12004,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="1" t="str" cm="1">
         <f t="array" ref="D37">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Incineration</v>
@@ -12076,7 +12022,7 @@
         <v>NGAF 2025 Table 18</v>
       </c>
     </row>
-    <row r="38" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="1" t="str" cm="1">
         <f t="array" ref="D38">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Incineration</v>
@@ -12094,7 +12040,7 @@
         <v>NGAF 2025 Table 18</v>
       </c>
     </row>
-    <row r="39" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D39" s="1" t="str" cm="1">
         <f t="array" ref="D39">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Composting</v>
@@ -12112,7 +12058,7 @@
         <v>NGAF 2025 Table 19</v>
       </c>
     </row>
-    <row r="40" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D40" s="1" t="str" cm="1">
         <f t="array" ref="D40">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Composting</v>
@@ -12130,7 +12076,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="1" t="str" cm="1">
         <f t="array" ref="D41">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Composting</v>
@@ -12148,7 +12094,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="1" t="str" cm="1">
         <f t="array" ref="D42">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Composting</v>
@@ -12166,7 +12112,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="1" t="str" cm="1">
         <f t="array" ref="D43">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Composting</v>
@@ -12184,7 +12130,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="1" t="str" cm="1">
         <f t="array" ref="D44">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Composting</v>
@@ -12202,7 +12148,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="1" t="str" cm="1">
         <f t="array" ref="D45">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Anaerobic digestion</v>
@@ -12220,7 +12166,7 @@
         <v>NGAF 2025 Table 19</v>
       </c>
     </row>
-    <row r="46" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" s="1" t="str" cm="1">
         <f t="array" ref="D46">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Anaerobic digestion</v>
@@ -12238,7 +12184,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="1" t="str" cm="1">
         <f t="array" ref="D47">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Anaerobic digestion</v>
@@ -12256,7 +12202,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D48" s="1" t="str" cm="1">
         <f t="array" ref="D48">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Anaerobic digestion</v>
@@ -12274,7 +12220,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D49" s="1" t="str" cm="1">
         <f t="array" ref="D49">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Anaerobic digestion</v>
@@ -12292,7 +12238,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D50" s="1" t="str" cm="1">
         <f t="array" ref="D50">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_EmissionFactorsForWasteTreatment_Data(), Table_SourceData_WasteSolid_WasteTreatmentEFs[[#Headers],[Treatment type t]], 0)</f>
         <v>Anaerobic digestion</v>
@@ -12310,38 +12256,38 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D52" s="5" t="str" cm="1">
         <f t="array" ref="D52">WasteSolid_SourceData.Waste_WasteVolumeToMassConversion_Title()</f>
         <v>Volume to mass conversion factor for various waste types</v>
       </c>
     </row>
-    <row r="53" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D53" s="4" t="str" cm="1">
         <f t="array" ref="D53">WasteSolid_SourceData.Waste_WasteVolumeToMassConversion_Source()</f>
         <v>VEERG 2026: Table A.4.1.2</v>
       </c>
     </row>
-    <row r="54" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D54" s="29" t="str" cm="1">
         <f t="array" ref="D54">WasteSolid_SourceData.Waste_WasteVolumeToMassConversion_Variation()</f>
         <v>VARIATION OF SOURCE: Changed column header CFw to VTMw to match title variable.</v>
       </c>
     </row>
-    <row r="55" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D55" s="1" t="str" cm="1">
         <f t="array" ref="D55">WasteSolid_SourceData.Waste_WasteVolumeToMassConversion_Variable()</f>
         <v>VTMw</v>
       </c>
     </row>
-    <row r="56" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D56" s="28" t="str" cm="1">
         <f t="array" ref="D56">WasteSolid_SourceData.Waste_WasteVolumeToMassConversion_Unit()</f>
         <v>t/m3</v>
       </c>
     </row>
-    <row r="57" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D57" s="24" t="s">
         <v>89</v>
       </c>
@@ -12349,7 +12295,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="58" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D58" s="24" t="str" cm="1">
         <f t="array" ref="D58">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_WasteVolumeToMassConversion_Data(), Table_SourceData_WasteSolid_VolumeToMassConversion[[#Headers],[Waste type w]], 0)</f>
         <v>Food waste (including animal carcasses, spoiled animal feed or crop)</v>
@@ -12359,7 +12305,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="59" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D59" s="1" t="str" cm="1">
         <f t="array" ref="D59">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_WasteVolumeToMassConversion_Data(), Table_SourceData_WasteSolid_VolumeToMassConversion[[#Headers],[Waste type w]], 0)</f>
         <v>Paper and cardboard</v>
@@ -12369,7 +12315,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="60" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D60" s="1" t="str" cm="1">
         <f t="array" ref="D60">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_WasteVolumeToMassConversion_Data(), Table_SourceData_WasteSolid_VolumeToMassConversion[[#Headers],[Waste type w]], 0)</f>
         <v>Green waste (including crop residues or prunings)</v>
@@ -12379,7 +12325,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="61" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D61" s="1" t="str" cm="1">
         <f t="array" ref="D61">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_WasteVolumeToMassConversion_Data(), Table_SourceData_WasteSolid_VolumeToMassConversion[[#Headers],[Waste type w]], 0)</f>
         <v>Wood</v>
@@ -12389,7 +12335,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="62" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D62" s="1" t="str" cm="1">
         <f t="array" ref="D62">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_WasteVolumeToMassConversion_Data(), Table_SourceData_WasteSolid_VolumeToMassConversion[[#Headers],[Waste type w]], 0)</f>
         <v>Textiles</v>
@@ -12399,7 +12345,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="63" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D63" s="1" t="str" cm="1">
         <f t="array" ref="D63">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_WasteVolumeToMassConversion_Data(), Table_SourceData_WasteSolid_VolumeToMassConversion[[#Headers],[Waste type w]], 0)</f>
         <v>Sludge</v>
@@ -12409,7 +12355,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="64" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D64" s="1" t="str" cm="1">
         <f t="array" ref="D64">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_WasteVolumeToMassConversion_Data(), Table_SourceData_WasteSolid_VolumeToMassConversion[[#Headers],[Waste type w]], 0)</f>
         <v>Rubber and leather</v>
@@ -12419,7 +12365,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="65" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D65" s="1" t="str" cm="1">
         <f t="array" ref="D65">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_WasteVolumeToMassConversion_Data(), Table_SourceData_WasteSolid_VolumeToMassConversion[[#Headers],[Waste type w]], 0)</f>
         <v>Inert waste (including concrete, metal, plastic or glass)</v>
@@ -12429,7 +12375,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="66" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D66" s="1" t="str" cm="1">
         <f t="array" ref="D66">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_WasteVolumeToMassConversion_Data(), Table_SourceData_WasteSolid_VolumeToMassConversion[[#Headers],[Waste type w]], 0)</f>
         <v>Municipal solid waste</v>
@@ -12439,7 +12385,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="67" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D67" s="1" t="str" cm="1">
         <f t="array" ref="D67">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_WasteVolumeToMassConversion_Data(), Table_SourceData_WasteSolid_VolumeToMassConversion[[#Headers],[Waste type w]], 0)</f>
         <v>Commercial and industrial waste</v>
@@ -12449,7 +12395,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="68" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D68" s="1" t="str" cm="1">
         <f t="array" ref="D68">Common_InputFunctions.Utility_DisplayArrayInTable(WasteSolid_SourceData.Waste_WasteVolumeToMassConversion_Data(), Table_SourceData_WasteSolid_VolumeToMassConversion[[#Headers],[Waste type w]], 0)</f>
         <v>Construction and demolition waste</v>
@@ -12459,103 +12405,103 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="69" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="4:5" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12577,7 +12523,7 @@
     <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:BY297"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="6" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" style="6" customWidth="1"/>
@@ -12610,10 +12556,10 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:65" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" s="8" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -12640,11 +12586,11 @@
       <c r="V3" s="9"/>
       <c r="W3" s="9"/>
     </row>
-    <row r="4" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4"/>
       <c r="BM4" s="2"/>
     </row>
-    <row r="5" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5"/>
       <c r="D5" s="5" t="str" cm="1">
         <f t="array" ref="D5">Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title()</f>
@@ -12652,7 +12598,7 @@
       </c>
       <c r="BM5" s="2"/>
     </row>
-    <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="73" t="s">
         <v>1</v>
       </c>
@@ -12666,7 +12612,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="54" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -12684,7 +12630,7 @@
         <v>NSW</v>
       </c>
     </row>
-    <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -12702,7 +12648,7 @@
         <v>ACT</v>
       </c>
     </row>
-    <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9"/>
       <c r="D9" s="24" t="str" cm="1">
         <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -12717,7 +12663,7 @@
         <v>VIC</v>
       </c>
     </row>
-    <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10"/>
       <c r="D10" s="24" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -12732,7 +12678,7 @@
         <v>QLD</v>
       </c>
     </row>
-    <row r="11" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
       <c r="D11" s="24" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -12748,7 +12694,7 @@
       </c>
       <c r="BM11" s="2"/>
     </row>
-    <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="D12" s="24" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -12764,7 +12710,7 @@
       </c>
       <c r="BM12" s="2"/>
     </row>
-    <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13"/>
       <c r="D13" s="24" t="str" cm="1">
         <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -12779,7 +12725,7 @@
         <v>TAS</v>
       </c>
     </row>
-    <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14"/>
       <c r="D14" s="24" t="str" cm="1">
         <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -12794,129 +12740,129 @@
         <v>NT</v>
       </c>
     </row>
-    <row r="15" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15"/>
     </row>
-    <row r="16" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16"/>
     </row>
-    <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17"/>
     </row>
-    <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18"/>
       <c r="D18" s="5" t="str" cm="1">
         <f t="array" ref="D18">Common_SourceData.Common_SourceData_WASA4Areas_Title()</f>
         <v>ABS Statistcal Areas Level 4 - Western Australia</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19"/>
       <c r="D19" s="4" t="str" cm="1">
         <f t="array" ref="D19">Common_SourceData.Common_SourceData_WASA4Areas_Source()</f>
         <v>Australian Bureau of Statistics (ABS) - Statistical Areas Level 2 - 2021 - Shapefile</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20"/>
       <c r="D20" s="24" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="24" t="str" cm="1">
         <f t="array" ref="D21">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Bunbury</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22"/>
       <c r="D22" s="24" t="str" cm="1">
         <f t="array" ref="D22">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Mandurah</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
       <c r="D23" s="24" t="str" cm="1">
         <f t="array" ref="D23">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - Inner</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
       <c r="D24" s="24" t="str" cm="1">
         <f t="array" ref="D24">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North East</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="D25" s="24" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North West</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
       <c r="D26" s="24" t="str" cm="1">
         <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South East</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
       <c r="D27" s="24" t="str" cm="1">
         <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South West</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
       <c r="D28" s="24" t="str" cm="1">
         <f t="array" ref="D28">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Wheat Belt</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
       <c r="D29" s="24" t="str" cm="1">
         <f t="array" ref="D29">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (North)</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="D30" s="24" t="str" cm="1">
         <f t="array" ref="D30">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (South)</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="D34" s="5" t="str" cm="1">
         <f t="array" ref="D34">Common_SourceData.Common_SourceData_GWP_Title()</f>
         <v>Global warming potential for greenhouse gases</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="D35" s="4" t="str" cm="1">
         <f t="array" ref="D35">Common_SourceData.Common_SourceData_GWP_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="D36" s="24" t="s">
         <v>10</v>
@@ -12925,7 +12871,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="D37" s="24" t="str" cm="1">
         <f t="array" ref="D37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -12936,7 +12882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="D38" s="24" t="str" cm="1">
         <f t="array" ref="D38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -12947,7 +12893,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="D39" s="24" t="str" cm="1">
         <f t="array" ref="D39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -12958,7 +12904,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="D40" s="24" t="str" cm="1">
         <f t="array" ref="D40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -12969,7 +12915,7 @@
         <v>6630</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
       <c r="D41" s="24" t="str" cm="1">
         <f t="array" ref="D41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -12980,7 +12926,7 @@
         <v>12200</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42"/>
       <c r="D42" s="24" t="str" cm="1">
         <f t="array" ref="D42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -12991,7 +12937,7 @@
         <v>22800</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43"/>
       <c r="D43" s="24" t="str" cm="1">
         <f t="array" ref="D43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -13002,24 +12948,24 @@
         <v>17200</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44"/>
     </row>
-    <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45"/>
       <c r="D45" s="5" t="str" cm="1">
         <f t="array" ref="D45">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Title()</f>
         <v>Factor to convert elemental mass of gas to molecular mass</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46"/>
       <c r="D46" s="4" t="str" cm="1">
         <f t="array" ref="D46">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47"/>
       <c r="D47" s="24" t="s">
         <v>10</v>
@@ -13037,7 +12983,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48"/>
       <c r="D48" s="24" t="str" cm="1">
         <f t="array" ref="D48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -13060,7 +13006,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49"/>
       <c r="D49" s="24" t="str" cm="1">
         <f t="array" ref="D49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -13083,7 +13029,7 @@
         <v>1.3333333333333333</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50"/>
       <c r="D50" s="24" t="str" cm="1">
         <f t="array" ref="D50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -13106,7 +13052,7 @@
         <v>1.5714285714285714</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51"/>
       <c r="D51" s="24" t="str" cm="1">
         <f t="array" ref="D51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -13129,7 +13075,7 @@
         <v>3.2857142857142856</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52"/>
       <c r="D52" s="24" t="str" cm="1">
         <f t="array" ref="D52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -13152,7 +13098,7 @@
         <v>2.3333333333333335</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53"/>
       <c r="D53" s="24" t="str" cm="1">
         <f t="array" ref="D53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -13175,7 +13121,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54"/>
       <c r="D54" s="24" t="str" cm="1">
         <f t="array" ref="D54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -13198,49 +13144,49 @@
         <v>1.1666666666666667</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57"/>
       <c r="D57" s="5" t="str" cm="1">
         <f t="array" ref="D57">Common_SourceData.Common_SourceData_WetAndDryZones_Title()</f>
         <v>VEERG Australian wet and dry zones</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58"/>
       <c r="D58" s="4" t="str" cm="1">
         <f t="array" ref="D58">Common_SourceData.Common_SourceData_WetAndDryZones_Source()</f>
         <v>VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59"/>
       <c r="D59" s="29" t="str" cm="1">
         <f t="array" ref="D59:D61">"⚠️" &amp; Common_SourceData.Common_SourceData_WetAndDryZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60"/>
       <c r="D60" s="29" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61"/>
       <c r="D61" s="29" t="str">
         <v>⚠️Fixed typo - Changed 'Fry' to 'Dry'.</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63"/>
       <c r="D63" s="24" t="s">
         <v>3</v>
@@ -13249,7 +13195,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64"/>
       <c r="D64" s="24" t="str" cm="1">
         <f t="array" ref="D64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -13260,7 +13206,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65"/>
       <c r="D65" s="24" t="str" cm="1">
         <f t="array" ref="D65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -13271,7 +13217,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66"/>
       <c r="D66" s="24" t="str" cm="1">
         <f t="array" ref="D66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -13282,7 +13228,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67"/>
       <c r="D67" s="24" t="str" cm="1">
         <f t="array" ref="D67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -13293,7 +13239,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68"/>
       <c r="D68" s="24" t="str" cm="1">
         <f t="array" ref="D68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -13304,7 +13250,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69"/>
       <c r="D69" s="24" t="str" cm="1">
         <f t="array" ref="D69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -13315,7 +13261,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70"/>
       <c r="D70" s="24" t="str" cm="1">
         <f t="array" ref="D70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -13326,7 +13272,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71"/>
       <c r="D71" s="24" t="str" cm="1">
         <f t="array" ref="D71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -13337,7 +13283,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72"/>
       <c r="D72" s="24" t="str" cm="1">
         <f t="array" ref="D72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -13348,7 +13294,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73"/>
       <c r="D73" s="24" t="str" cm="1">
         <f t="array" ref="D73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -13359,7 +13305,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74"/>
       <c r="D74" s="24" t="str" cm="1">
         <f t="array" ref="D74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -13370,7 +13316,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75"/>
       <c r="D75" s="24" t="str" cm="1">
         <f t="array" ref="D75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -13381,7 +13327,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76"/>
       <c r="D76" s="24" t="str" cm="1">
         <f t="array" ref="D76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -13392,7 +13338,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77"/>
       <c r="D77" s="24" t="str" cm="1">
         <f t="array" ref="D77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -13403,64 +13349,64 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78"/>
     </row>
-    <row r="79" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79"/>
     </row>
-    <row r="80" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80"/>
     </row>
-    <row r="81" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81"/>
       <c r="D81" s="5" t="str" cm="1">
         <f t="array" ref="D81">Common_SourceData.Common_SourceData_ClimateZones_Title()</f>
         <v>VEERG Australian climate zones</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82"/>
       <c r="D82" s="4" t="str" cm="1">
         <f t="array" ref="D82">Common_SourceData.Common_SourceData_ClimateZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83"/>
       <c r="D83" s="29" t="str" cm="1">
         <f t="array" ref="D83:D87">"⚠️" &amp; Common_SourceData.Common_SourceData_ClimateZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84"/>
       <c r="D84" s="29" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85"/>
       <c r="D85" s="29" t="str">
         <v>⚠️Fixed typo in MAT value for warm temperate dry - changed 10 to 11.</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86"/>
       <c r="D86" s="29" t="str">
         <v>⚠️Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87"/>
       <c r="D87" s="29" t="str">
         <v>⚠️GAF accepts rainfall as a proxy for precipitation.</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88"/>
     </row>
-    <row r="89" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89"/>
       <c r="D89" s="24" t="s">
         <v>3</v>
@@ -13512,7 +13458,7 @@
       </c>
       <c r="T89" s="24"/>
     </row>
-    <row r="90" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90"/>
       <c r="D90" s="24" t="str" cm="1">
         <f t="array" ref="D90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -13580,7 +13526,7 @@
       </c>
       <c r="T90" s="24"/>
     </row>
-    <row r="91" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91"/>
       <c r="D91" s="24" t="str" cm="1">
         <f t="array" ref="D91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -13648,7 +13594,7 @@
       </c>
       <c r="T91" s="24"/>
     </row>
-    <row r="92" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92"/>
       <c r="D92" s="24" t="str" cm="1">
         <f t="array" ref="D92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -13716,7 +13662,7 @@
       </c>
       <c r="T92" s="24"/>
     </row>
-    <row r="93" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93"/>
       <c r="D93" s="24" t="str" cm="1">
         <f t="array" ref="D93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -13784,7 +13730,7 @@
       </c>
       <c r="T93" s="24"/>
     </row>
-    <row r="94" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94"/>
       <c r="D94" s="24" t="str" cm="1">
         <f t="array" ref="D94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -13852,7 +13798,7 @@
       </c>
       <c r="T94" s="24"/>
     </row>
-    <row r="95" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95"/>
       <c r="D95" s="24" t="str" cm="1">
         <f t="array" ref="D95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -13920,7 +13866,7 @@
       </c>
       <c r="T95" s="24"/>
     </row>
-    <row r="96" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96"/>
       <c r="D96" s="24" t="str" cm="1">
         <f t="array" ref="D96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -13988,7 +13934,7 @@
       </c>
       <c r="T96" s="24"/>
     </row>
-    <row r="97" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97"/>
       <c r="D97" s="24" t="str" cm="1">
         <f t="array" ref="D97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -14056,66 +14002,66 @@
       </c>
       <c r="T97" s="24"/>
     </row>
-    <row r="98" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98"/>
     </row>
-    <row r="99" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99"/>
       <c r="D99" s="28" t="str" cm="1">
         <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100"/>
       <c r="D100" s="28" t="str">
         <v>MAT = mean annual temperature</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101"/>
       <c r="D101" s="28" t="str">
         <v>MAP = mean annual precipitation</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102"/>
       <c r="D102" s="28" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103"/>
       <c r="D103" s="28"/>
     </row>
-    <row r="104" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104"/>
     </row>
-    <row r="105" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105"/>
       <c r="D105" s="5" t="str" cm="1">
         <f t="array" ref="D105">Common_SourceData.Common_SourceData_TemperatureZones_Title()</f>
         <v>VEERG Australian temperature zones</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106"/>
       <c r="D106" s="4" t="str" cm="1">
         <f t="array" ref="D106">Common_SourceData.Common_SourceData_TemperatureZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107"/>
       <c r="D107" s="29" t="str" cm="1">
         <f t="array" ref="D107">"⚠️" &amp; Common_SourceData.Common_SourceData_TemperatureZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109"/>
       <c r="D109" s="24" t="s">
         <v>35</v>
@@ -14130,7 +14076,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110"/>
       <c r="D110" s="24" t="str" cm="1">
         <f t="array" ref="D110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -14149,7 +14095,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111"/>
       <c r="D111" s="24" t="str" cm="1">
         <f t="array" ref="D111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -14168,7 +14114,7 @@
         <v>25.998999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112"/>
       <c r="D112" s="24" t="str" cm="1">
         <f t="array" ref="D112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -14187,13 +14133,13 @@
         <v>14.999000000000001</v>
       </c>
     </row>
-    <row r="113" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113"/>
     </row>
-    <row r="114" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114"/>
     </row>
-    <row r="115" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115"/>
       <c r="D115" s="5" t="str" cm="1">
         <f t="array" ref="D115">Common_SourceData.Common_SourceData_RainfallZones_Title()</f>
@@ -14201,7 +14147,7 @@
       </c>
       <c r="BN115" s="6"/>
     </row>
-    <row r="116" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116"/>
       <c r="D116" s="4" t="str" cm="1">
         <f t="array" ref="D116">Common_SourceData.Common_SourceData_RainfallZones_Source()</f>
@@ -14209,7 +14155,7 @@
       </c>
       <c r="BN116" s="6"/>
     </row>
-    <row r="117" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117"/>
       <c r="D117" s="29" t="str" cm="1">
         <f t="array" ref="D117">"⚠️" &amp; Common_SourceData.Common_SourceData_RainfallZones_Variation()</f>
@@ -14217,11 +14163,11 @@
       </c>
       <c r="BN117" s="6"/>
     </row>
-    <row r="118" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118"/>
       <c r="BN118" s="6"/>
     </row>
-    <row r="119" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119"/>
       <c r="D119" s="24" t="s">
         <v>38</v>
@@ -14237,7 +14183,7 @@
       </c>
       <c r="BN119" s="6"/>
     </row>
-    <row r="120" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120"/>
       <c r="D120" s="24" t="str" cm="1">
         <f t="array" ref="D120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -14257,7 +14203,7 @@
       </c>
       <c r="BN120" s="6"/>
     </row>
-    <row r="121" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121"/>
       <c r="D121" s="24" t="str" cm="1">
         <f t="array" ref="D121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -14277,31 +14223,31 @@
       </c>
       <c r="BN121" s="6"/>
     </row>
-    <row r="122" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122"/>
       <c r="BN122" s="6"/>
     </row>
-    <row r="123" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123"/>
     </row>
-    <row r="124" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124"/>
       <c r="D124" s="5" t="str" cm="1">
         <f t="array" ref="D124">Common_SourceData.Common_SourceData_LeachingZones_Title()</f>
         <v>VEERG Australian leaching zones</v>
       </c>
     </row>
-    <row r="125" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125"/>
       <c r="D125" s="4" t="str" cm="1">
         <f t="array" ref="D125">Common_SourceData.Common_SourceData_LeachingZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="126" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126"/>
     </row>
-    <row r="127" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127"/>
       <c r="D127" s="24" t="s">
         <v>40</v>
@@ -14310,7 +14256,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="128" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128"/>
       <c r="D128" s="24" t="str" cm="1">
         <f t="array" ref="D128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -14321,7 +14267,7 @@
         <v>Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="129" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129"/>
       <c r="D129" s="24" t="str" cm="1">
         <f t="array" ref="D129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -14332,13 +14278,13 @@
         <v>Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="130" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130"/>
     </row>
-    <row r="131" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131"/>
     </row>
-    <row r="132" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132"/>
       <c r="D132" s="5" t="str" cm="1">
         <f t="array" ref="D132">Common_SourceData.Common_SourceData_FracWET_Title()</f>
@@ -14346,7 +14292,7 @@
       </c>
       <c r="E132" s="16"/>
     </row>
-    <row r="133" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133"/>
       <c r="D133" s="4" t="str" cm="1">
         <f t="array" ref="D133">Common_SourceData.Common_SourceData_FracWET_Source()</f>
@@ -14354,7 +14300,7 @@
       </c>
       <c r="E133" s="16"/>
     </row>
-    <row r="134" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134"/>
       <c r="D134" t="s">
         <v>46</v>
@@ -14363,7 +14309,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="135" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135"/>
       <c r="D135" t="str" cm="1">
         <f t="array" ref="D135">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -14374,7 +14320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136"/>
       <c r="D136" s="1" t="str" cm="1">
         <f t="array" ref="D136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -14385,10 +14331,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137"/>
     </row>
-    <row r="138" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138"/>
       <c r="BN138" s="6"/>
       <c r="BO138" s="6"/>
@@ -14403,7 +14349,7 @@
       <c r="BX138" s="6"/>
       <c r="BY138" s="6"/>
     </row>
-    <row r="139" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139"/>
       <c r="D139" s="5" t="str" cm="1">
         <f t="array" ref="D139">Common_SourceData.Common_SourceData_FracWETIrrigation_Title()</f>
@@ -14422,7 +14368,7 @@
       <c r="BX139" s="6"/>
       <c r="BY139" s="6"/>
     </row>
-    <row r="140" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140"/>
       <c r="D140" s="4" t="str" cm="1">
         <f t="array" ref="D140">Common_SourceData.Common_SourceData_FracWETIrrigation_Source()</f>
@@ -14441,7 +14387,7 @@
       <c r="BX140" s="6"/>
       <c r="BY140" s="6"/>
     </row>
-    <row r="141" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141"/>
       <c r="D141" s="29" t="str" cm="1">
         <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
@@ -14449,7 +14395,7 @@
       </c>
       <c r="BN141" s="6"/>
     </row>
-    <row r="142" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142"/>
       <c r="D142" s="24" t="s">
         <v>56</v>
@@ -14459,7 +14405,7 @@
       </c>
       <c r="BN142" s="6"/>
     </row>
-    <row r="143" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143"/>
       <c r="D143" s="24" t="str" cm="1">
         <f t="array" ref="D143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -14471,7 +14417,7 @@
       </c>
       <c r="BN143" s="6"/>
     </row>
-    <row r="144" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144"/>
       <c r="D144" s="1" t="str" cm="1">
         <f t="array" ref="D144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -14483,7 +14429,7 @@
       </c>
       <c r="BN144" s="6"/>
     </row>
-    <row r="145" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145"/>
       <c r="D145" s="1" t="str" cm="1">
         <f t="array" ref="D145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -14495,7 +14441,7 @@
       </c>
       <c r="BN145" s="6"/>
     </row>
-    <row r="146" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146"/>
       <c r="D146" s="1" t="str" cm="1">
         <f t="array" ref="D146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -14507,7 +14453,7 @@
       </c>
       <c r="BN146" s="6"/>
     </row>
-    <row r="147" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147"/>
       <c r="D147" s="1" t="str" cm="1">
         <f t="array" ref="D147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -14519,15 +14465,15 @@
       </c>
       <c r="BN147" s="6"/>
     </row>
-    <row r="148" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148"/>
       <c r="BN148" s="6"/>
     </row>
-    <row r="149" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149"/>
       <c r="BN149" s="6"/>
     </row>
-    <row r="150" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150"/>
       <c r="D150" s="5" t="str" cm="1">
         <f t="array" ref="D150">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
@@ -14535,7 +14481,7 @@
       </c>
       <c r="BN150" s="6"/>
     </row>
-    <row r="151" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151"/>
       <c r="D151" s="4" t="str" cm="1">
         <f t="array" ref="D151">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
@@ -14543,11 +14489,11 @@
       </c>
       <c r="BN151" s="6"/>
     </row>
-    <row r="152" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152"/>
       <c r="BN152" s="6"/>
     </row>
-    <row r="153" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153"/>
       <c r="D153" s="24" t="s">
         <v>42</v>
@@ -14567,7 +14513,7 @@
       <c r="BL153" s="2"/>
       <c r="BM153" s="2"/>
     </row>
-    <row r="154" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154"/>
       <c r="D154" s="24" t="str" cm="1">
         <f t="array" ref="D154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -14589,7 +14535,7 @@
       <c r="BL154" s="2"/>
       <c r="BM154" s="2"/>
     </row>
-    <row r="155" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155"/>
       <c r="D155" s="24" t="str" cm="1">
         <f t="array" ref="D155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -14611,7 +14557,7 @@
       <c r="BL155" s="2"/>
       <c r="BM155" s="2"/>
     </row>
-    <row r="156" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156"/>
       <c r="D156" s="24" t="str" cm="1">
         <f t="array" ref="D156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -14622,7 +14568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157"/>
       <c r="D157" s="24" t="str" cm="1">
         <f t="array" ref="D157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -14633,7 +14579,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158"/>
       <c r="D158" s="24" t="str" cm="1">
         <f t="array" ref="D158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -14644,34 +14590,34 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159"/>
     </row>
-    <row r="160" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160"/>
     </row>
-    <row r="161" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D161" s="5" t="str" cm="1">
         <f t="array" ref="D161">Common_SourceData.Common_SourceData_FracLEACH_Title()</f>
         <v>Fraction of N that is available for leaching and runoff</v>
       </c>
       <c r="E161" s="16"/>
     </row>
-    <row r="162" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D162" s="4" t="str" cm="1">
         <f t="array" ref="D162">Common_SourceData.Common_SourceData_FracLEACH_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
       <c r="E162" s="16"/>
     </row>
-    <row r="163" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D163" s="4" t="str" cm="1">
         <f t="array" ref="D163">Common_SourceData.Common_SourceData_FracLEACH_NIRReference()</f>
         <v>National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)</v>
       </c>
       <c r="E163" s="16"/>
     </row>
-    <row r="164" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D164" s="16" t="str" cm="1">
         <f t="array" ref="D164:E164">Common_SourceData.Common_SourceData_FracLEACH_Data()</f>
         <v>FracLEACH</v>
@@ -14680,17 +14626,17 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="165" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN165" s="6"/>
       <c r="BO165" s="6"/>
       <c r="BP165" s="6"/>
     </row>
-    <row r="166" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN166" s="6"/>
       <c r="BO166" s="6"/>
       <c r="BP166" s="6"/>
     </row>
-    <row r="167" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D167" s="5" t="str" cm="1">
         <f t="array" ref="D167">Common_SourceData.Common_SourceData_EFleach_Title()</f>
         <v>Emission factor for nitrogen leaching and runoff</v>
@@ -14699,7 +14645,7 @@
       <c r="BO167" s="6"/>
       <c r="BP167" s="6"/>
     </row>
-    <row r="168" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D168" s="4" t="str" cm="1">
         <f t="array" ref="D168">Common_SourceData.Common_SourceData_EFleach_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
@@ -14708,7 +14654,7 @@
       <c r="BO168" s="6"/>
       <c r="BP168" s="6"/>
     </row>
-    <row r="169" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D169" s="4" t="str" cm="1">
         <f t="array" ref="D169">Common_SourceData.Common_SourceData_EFleach_NIRReference()</f>
         <v>National Inventory Report Volume 1: Equation 3.D.B_10</v>
@@ -14717,7 +14663,7 @@
       <c r="BO169" s="6"/>
       <c r="BP169" s="6"/>
     </row>
-    <row r="170" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D170" s="1" t="str" cm="1">
         <f t="array" ref="D170:E170">Common_SourceData.Common_SourceData_EFleach_Data()</f>
         <v>EFleach</v>
@@ -14729,17 +14675,17 @@
       <c r="BO170" s="6"/>
       <c r="BP170" s="6"/>
     </row>
-    <row r="171" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN171" s="6"/>
       <c r="BO171" s="6"/>
       <c r="BP171" s="6"/>
     </row>
-    <row r="172" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN172" s="6"/>
       <c r="BO172" s="6"/>
       <c r="BP172" s="6"/>
     </row>
-    <row r="173" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D173" s="5" t="str" cm="1">
         <f t="array" ref="D173">Common_SourceData.Common_SourceData_DensityOfMethane_Title()</f>
         <v>p = density of methane</v>
@@ -14748,7 +14694,7 @@
       <c r="BO173" s="6"/>
       <c r="BP173" s="6"/>
     </row>
-    <row r="174" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D174" s="4" t="str" cm="1">
         <f t="array" ref="D174">Common_SourceData.Common_SourceData_DensityOfMethane_Source()</f>
         <v>National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2</v>
@@ -14757,7 +14703,7 @@
       <c r="BO174" s="6"/>
       <c r="BP174" s="6"/>
     </row>
-    <row r="175" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D175" s="1" cm="1">
         <f t="array" ref="D175">Common_SourceData.Common_SourceData_DensityOfMethane_Data()</f>
         <v>0.6784</v>
@@ -14770,17 +14716,17 @@
       <c r="BO175" s="6"/>
       <c r="BP175" s="6"/>
     </row>
-    <row r="176" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN176" s="6"/>
       <c r="BO176" s="6"/>
       <c r="BP176" s="6"/>
     </row>
-    <row r="177" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN177" s="6"/>
       <c r="BO177" s="6"/>
       <c r="BP177" s="6"/>
     </row>
-    <row r="178" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D178" s="5" t="str" cm="1">
         <f t="array" ref="D178">Common_SourceData.Common_SourceData_EFN2O_Title()</f>
         <v>Nitrous oxide emission factors for inorganic fertiliser application</v>
@@ -14789,7 +14735,7 @@
       <c r="BO178" s="6"/>
       <c r="BP178" s="6"/>
     </row>
-    <row r="179" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D179" s="4" t="str" cm="1">
         <f t="array" ref="D179">Common_SourceData.Common_SourceData_EFN2O_Source()</f>
         <v>VEERG 2026: Table A.2.2.1</v>
@@ -14798,39 +14744,39 @@
       <c r="BO179" s="6"/>
       <c r="BP179" s="6"/>
     </row>
-    <row r="180" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D180" s="28" t="str" cm="1">
         <f t="array" ref="D180">Common_SourceData.Common_SourceData_EFN2O_Unit()</f>
         <v>(kg N2O-N / kg N</v>
       </c>
     </row>
-    <row r="181" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D181" s="29" t="str" cm="1">
         <f t="array" ref="D181:D185">Common_SourceData.Common_SourceData_EFN2O_Variation()</f>
         <v>VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="182" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D182" s="29" t="str">
         <v>Removed duplicate 'Aquaculture' row.</v>
       </c>
     </row>
-    <row r="183" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D183" s="29" t="str">
         <v>Removed asterisks to aid lookup.</v>
       </c>
     </row>
-    <row r="184" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D184" s="29" t="str">
         <v>Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.</v>
       </c>
     </row>
-    <row r="185" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D185" s="29" t="str">
         <v>Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup.</v>
       </c>
     </row>
-    <row r="186" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D186" s="24" t="s">
         <v>50</v>
       </c>
@@ -14847,7 +14793,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D187" s="24" t="str" cm="1">
         <f t="array" ref="D187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated pasture</v>
@@ -14869,7 +14815,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="188" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D188" s="24" t="str" cm="1">
         <f t="array" ref="D188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated crop</v>
@@ -14891,7 +14837,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="189" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D189" s="24" t="str" cm="1">
         <f t="array" ref="D189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -14913,7 +14859,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="190" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D190" s="24" t="str" cm="1">
         <f t="array" ref="D190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -14935,7 +14881,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="191" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D191" s="24" t="str" cm="1">
         <f t="array" ref="D191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (low rainfall)</v>
@@ -14957,7 +14903,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="192" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D192" s="24" t="str" cm="1">
         <f t="array" ref="D192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (high rainfall)</v>
@@ -14979,7 +14925,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="193" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D193" s="24" t="str" cm="1">
         <f t="array" ref="D193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Sugar</v>
@@ -15001,7 +14947,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="194" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D194" s="24" t="str" cm="1">
         <f t="array" ref="D194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Cotton</v>
@@ -15023,7 +14969,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="195" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D195" s="24" t="str" cm="1">
         <f t="array" ref="D195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Horticultural crops</v>
@@ -15045,7 +14991,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="196" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D196" s="24" t="str" cm="1">
         <f t="array" ref="D196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (continuous flooding)</v>
@@ -15067,7 +15013,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="197" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D197" s="24" t="str" cm="1">
         <f t="array" ref="D197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (single and multiple drainage, or alternate wetting and drying)</v>
@@ -15089,7 +15035,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="198" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D198" s="24" t="str" cm="1">
         <f t="array" ref="D198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Aquaculture</v>
@@ -15111,7 +15057,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="199" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D199" s="24" t="str" cm="1">
         <f t="array" ref="D199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Forestry</v>
@@ -15133,31 +15079,31 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="202" spans="4:8" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D202" s="5" t="str" cm="1">
         <f t="array" ref="D202">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Title()</f>
         <v>Emission factor for urine and dung deposited on pasture, range or paddock</v>
       </c>
     </row>
-    <row r="203" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D203" s="4" t="str" cm="1">
         <f t="array" ref="D203">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source()</f>
         <v>VEERG 2026: Table A.2.2.2</v>
       </c>
     </row>
-    <row r="204" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D204" s="29" t="str" cm="1">
         <f t="array" ref="D204">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.</v>
       </c>
     </row>
-    <row r="205" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D205" s="28" t="str" cm="1">
         <f t="array" ref="D205">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="206" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D206" s="24" t="s">
         <v>3</v>
       </c>
@@ -15165,7 +15111,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="207" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D207" s="24" t="str" cm="1">
         <f t="array" ref="D207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -15175,7 +15121,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="208" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D208" s="1" t="str" cm="1">
         <f t="array" ref="D208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -15185,13 +15131,13 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="211" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D211" s="1" t="str" cm="1">
         <f t="array" ref="D211">Common_SourceData.Common_SourceData_MonthsToSeasons_Title()</f>
         <v>Months to Seasons Mapping</v>
       </c>
     </row>
-    <row r="212" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D212" s="24" t="s">
         <v>55</v>
       </c>
@@ -15199,7 +15145,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="213" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D213" s="24" t="str" cm="1">
         <f t="array" ref="D213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>January</v>
@@ -15209,7 +15155,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="214" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D214" s="1" t="str" cm="1">
         <f t="array" ref="D214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>February</v>
@@ -15219,7 +15165,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="215" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D215" s="1" t="str" cm="1">
         <f t="array" ref="D215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>March</v>
@@ -15229,7 +15175,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="216" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D216" s="1" t="str" cm="1">
         <f t="array" ref="D216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>April</v>
@@ -15239,7 +15185,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="217" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D217" s="1" t="str" cm="1">
         <f t="array" ref="D217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>May</v>
@@ -15249,7 +15195,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="218" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D218" s="1" t="str" cm="1">
         <f t="array" ref="D218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>June</v>
@@ -15259,7 +15205,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="219" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D219" s="1" t="str" cm="1">
         <f t="array" ref="D219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>July</v>
@@ -15269,7 +15215,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="220" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D220" s="1" t="str" cm="1">
         <f t="array" ref="D220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>August</v>
@@ -15279,7 +15225,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="221" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D221" s="1" t="str" cm="1">
         <f t="array" ref="D221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>September</v>
@@ -15289,7 +15235,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="222" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D222" s="1" t="str" cm="1">
         <f t="array" ref="D222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>October</v>
@@ -15299,7 +15245,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="223" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D223" s="1" t="str" cm="1">
         <f t="array" ref="D223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>November</v>
@@ -15309,7 +15255,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="224" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D224" s="1" t="str" cm="1">
         <f t="array" ref="D224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>December</v>
@@ -15319,25 +15265,25 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="227" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D227" s="5" t="str" cm="1">
         <f t="array" ref="D227">Common_SourceData.Common_SourceData_MCFTemperatureZone_Title()</f>
         <v>Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)</v>
       </c>
     </row>
-    <row r="228" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D228" s="4" t="str" cm="1">
         <f t="array" ref="D228">Common_SourceData.Common_SourceData_MCFTemperatureZone_Source()</f>
         <v>VEERG 2026: Table A.1.8.1</v>
       </c>
     </row>
-    <row r="229" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D229" s="29" t="str" cm="1">
         <f t="array" ref="D229">Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation()</f>
         <v>VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.</v>
       </c>
     </row>
-    <row r="231" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D231" s="24" t="s">
         <v>34</v>
       </c>
@@ -15387,7 +15333,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="232" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D232" s="24" t="str" cm="1">
         <f t="array" ref="D232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -15453,7 +15399,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D233" s="1" t="str" cm="1">
         <f t="array" ref="D233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -15519,7 +15465,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="234" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D234" s="1" t="str" cm="1">
         <f t="array" ref="D234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -15585,7 +15531,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="235" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D235" s="1" t="str" cm="1">
         <f t="array" ref="D235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -15651,7 +15597,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="236" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D236" s="1" t="str" cm="1">
         <f t="array" ref="D236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -15717,7 +15663,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D237" s="1" t="str" cm="1">
         <f t="array" ref="D237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -15783,7 +15729,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D238" s="1" t="str" cm="1">
         <f t="array" ref="D238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -15849,7 +15795,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="239" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D239" s="1" t="str" cm="1">
         <f t="array" ref="D239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -15915,7 +15861,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D240" s="1" t="str" cm="1">
         <f t="array" ref="D240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -15981,7 +15927,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D241" s="1" t="str" cm="1">
         <f t="array" ref="D241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -16047,7 +15993,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="242" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D242" s="1" t="str" cm="1">
         <f t="array" ref="D242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -16113,7 +16059,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="243" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D243" s="1" t="str" cm="1">
         <f t="array" ref="D243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -16179,7 +16125,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D244" s="1" t="str" cm="1">
         <f t="array" ref="D244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -16245,7 +16191,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="245" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D245" s="1" t="str" cm="1">
         <f t="array" ref="D245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -16311,7 +16257,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="246" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D246" s="1" t="str" cm="1">
         <f t="array" ref="D246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -16377,7 +16323,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="247" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D247" s="1" t="str" cm="1">
         <f t="array" ref="D247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -16443,7 +16389,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D248" s="1" t="str" cm="1">
         <f t="array" ref="D248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -16509,7 +16455,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="249" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D249" s="1" t="str" cm="1">
         <f t="array" ref="D249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -16575,7 +16521,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="250" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D250" s="1" t="str" cm="1">
         <f t="array" ref="D250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -16641,31 +16587,31 @@
         <v>28</v>
       </c>
     </row>
-    <row r="253" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D253" s="5" t="str" cm="1">
         <f t="array" ref="D253">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title()</f>
         <v>Emission factor for organic fertiliser and crop residues returned to the soil</v>
       </c>
     </row>
-    <row r="254" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D254" s="4" t="str" cm="1">
         <f t="array" ref="D254">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source()</f>
         <v>VEERG 2026: Table A.2.1.4</v>
       </c>
     </row>
-    <row r="255" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D255" s="1" t="str" cm="1">
         <f t="array" ref="D255">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable()</f>
         <v>EFNi &amp; EFN2Oi</v>
       </c>
     </row>
-    <row r="256" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D256" s="28" t="str" cm="1">
         <f t="array" ref="D256">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="257" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D257" s="24" t="s">
         <v>77</v>
       </c>
@@ -16673,7 +16619,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="258" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D258" s="24" t="str" cm="1">
         <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -16683,7 +16629,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="259" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D259" s="1" t="str" cm="1">
         <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -16693,17 +16639,17 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="263" spans="4:6" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:6" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D263" s="5" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="264" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D264" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="265" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D265" s="24" t="s">
         <v>85</v>
       </c>
@@ -16714,7 +16660,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="266" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D266" s="24" t="s">
         <v>166</v>
       </c>
@@ -16725,7 +16671,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D267" s="24" t="s">
         <v>168</v>
       </c>
@@ -16736,7 +16682,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D268" s="24" t="s">
         <v>170</v>
       </c>
@@ -16747,7 +16693,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="269" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D269" s="24" t="s">
         <v>172</v>
       </c>
@@ -16758,7 +16704,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D270" s="24" t="s">
         <v>174</v>
       </c>
@@ -16769,12 +16715,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D273" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="274" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D274" s="24" t="s">
         <v>85</v>
       </c>
@@ -16785,7 +16731,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="275" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D275" s="24" t="s">
         <v>177</v>
       </c>
@@ -16796,7 +16742,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D276" s="24" t="s">
         <v>179</v>
       </c>
@@ -16807,7 +16753,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="277" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D277" s="24" t="s">
         <v>181</v>
       </c>
@@ -16818,7 +16764,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="278" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D278" s="24" t="s">
         <v>183</v>
       </c>
@@ -16829,7 +16775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="279" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D279" s="24" t="s">
         <v>185</v>
       </c>
@@ -16840,12 +16786,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D282" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="283" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D283" s="24" t="s">
         <v>85</v>
       </c>
@@ -16856,7 +16802,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="284" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D284" s="24" t="s">
         <v>188</v>
       </c>
@@ -16867,7 +16813,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D285" s="24" t="s">
         <v>190</v>
       </c>
@@ -16878,7 +16824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D286" s="24" t="s">
         <v>192</v>
       </c>
@@ -16889,7 +16835,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="287" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D287" s="24" t="s">
         <v>194</v>
       </c>
@@ -16900,7 +16846,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="288" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D288" s="24" t="s">
         <v>196</v>
       </c>
@@ -16911,12 +16857,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D291" s="1" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="292" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D292" s="24" t="s">
         <v>85</v>
       </c>
@@ -16927,7 +16873,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="293" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D293" s="24" t="s">
         <v>199</v>
       </c>
@@ -16938,7 +16884,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D294" s="24" t="s">
         <v>201</v>
       </c>
@@ -16949,7 +16895,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="295" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D295" s="24" t="s">
         <v>203</v>
       </c>
@@ -16960,7 +16906,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="296" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D296" s="24" t="s">
         <v>205</v>
       </c>
@@ -16971,7 +16917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="297" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D297" s="24" t="s">
         <v>207</v>
       </c>
